--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/48.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/48.xlsx
@@ -426,13 +426,13 @@
         <v>-7.560399108616618</v>
       </c>
       <c r="E2">
-        <v>-16.3413039411446</v>
+        <v>-15.56055879443017</v>
       </c>
       <c r="F2">
-        <v>4.676126386249076</v>
+        <v>1.337717946022372</v>
       </c>
       <c r="G2">
-        <v>-16.07703133983301</v>
+        <v>-15.81608563287504</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.757741297063493</v>
       </c>
       <c r="E3">
-        <v>-16.15353529489056</v>
+        <v>-16.08263750582647</v>
       </c>
       <c r="F3">
-        <v>4.583831346963961</v>
+        <v>2.31153175414022</v>
       </c>
       <c r="G3">
-        <v>-16.38177807338799</v>
+        <v>-14.11533006196806</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.852136886668633</v>
       </c>
       <c r="E4">
-        <v>-16.83741185410691</v>
+        <v>-17.1571583468405</v>
       </c>
       <c r="F4">
-        <v>4.189914482441101</v>
+        <v>1.681815138206064</v>
       </c>
       <c r="G4">
-        <v>-15.57595271426864</v>
+        <v>-15.00870333412574</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.930800116591164</v>
       </c>
       <c r="E5">
-        <v>-16.66615855255884</v>
+        <v>-19.58391775433696</v>
       </c>
       <c r="F5">
-        <v>4.171027705657272</v>
+        <v>3.008086022336657</v>
       </c>
       <c r="G5">
-        <v>-14.39111509342861</v>
+        <v>-13.66912822637464</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.007403159084102</v>
       </c>
       <c r="E6">
-        <v>-16.41799817693851</v>
+        <v>-19.33606984342315</v>
       </c>
       <c r="F6">
-        <v>4.292458083233652</v>
+        <v>2.09961549168644</v>
       </c>
       <c r="G6">
-        <v>-13.84060158384966</v>
+        <v>-13.81854029069473</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.122288867328617</v>
       </c>
       <c r="E7">
-        <v>-18.06214217795537</v>
+        <v>-19.96868860534669</v>
       </c>
       <c r="F7">
-        <v>4.405798624754291</v>
+        <v>2.443825341836912</v>
       </c>
       <c r="G7">
-        <v>-14.02325898501005</v>
+        <v>-13.59692822718061</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.294817660756598</v>
       </c>
       <c r="E8">
-        <v>-18.02063418520106</v>
+        <v>-19.1908643243672</v>
       </c>
       <c r="F8">
-        <v>3.513005775569457</v>
+        <v>2.096797385782116</v>
       </c>
       <c r="G8">
-        <v>-12.84721831917089</v>
+        <v>-12.84131540158545</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.55612072000234</v>
       </c>
       <c r="E9">
-        <v>-17.90417089067179</v>
+        <v>-18.84056874597787</v>
       </c>
       <c r="F9">
-        <v>4.359602231434969</v>
+        <v>2.382219658090713</v>
       </c>
       <c r="G9">
-        <v>-12.64061292245889</v>
+        <v>-12.17390837395127</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.9221916339544084</v>
       </c>
       <c r="E10">
-        <v>-20.18158122539529</v>
+        <v>-21.40819086595693</v>
       </c>
       <c r="F10">
-        <v>4.272723058229356</v>
+        <v>2.405602813136938</v>
       </c>
       <c r="G10">
-        <v>-11.50372215165625</v>
+        <v>-10.27513764437492</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.406304427761942</v>
       </c>
       <c r="E11">
-        <v>-20.08658742613639</v>
+        <v>-23.21590787660485</v>
       </c>
       <c r="F11">
-        <v>4.244618208987174</v>
+        <v>2.029721163707829</v>
       </c>
       <c r="G11">
-        <v>-12.07255800242315</v>
+        <v>-12.68509644314029</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.01279525145364747</v>
       </c>
       <c r="E12">
-        <v>-22.80959507474063</v>
+        <v>-22.76816406604446</v>
       </c>
       <c r="F12">
-        <v>3.991909822149935</v>
+        <v>1.883169716274151</v>
       </c>
       <c r="G12">
-        <v>-10.12500207070097</v>
+        <v>-10.81491499701138</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.2598700494401956</v>
       </c>
       <c r="E13">
-        <v>-23.23274927143937</v>
+        <v>-23.52925110709159</v>
       </c>
       <c r="F13">
-        <v>4.396520909842937</v>
+        <v>2.469276101920525</v>
       </c>
       <c r="G13">
-        <v>-10.09246219649596</v>
+        <v>-8.86118052509277</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.409974040577983</v>
       </c>
       <c r="E14">
-        <v>-21.69464854626013</v>
+        <v>-22.859403760351</v>
       </c>
       <c r="F14">
-        <v>4.102763604727371</v>
+        <v>2.577921457002097</v>
       </c>
       <c r="G14">
-        <v>-9.378780101208935</v>
+        <v>-8.643222101785096</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.4449943145677394</v>
       </c>
       <c r="E15">
-        <v>-23.2184800498412</v>
+        <v>-24.36393037923737</v>
       </c>
       <c r="F15">
-        <v>4.437833248955354</v>
+        <v>2.482884521613715</v>
       </c>
       <c r="G15">
-        <v>-9.177398409219576</v>
+        <v>-8.913453665756284</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.3750978814040711</v>
       </c>
       <c r="E16">
-        <v>-25.43367820864732</v>
+        <v>-26.56121842334316</v>
       </c>
       <c r="F16">
-        <v>4.79554880124107</v>
+        <v>2.520634880894094</v>
       </c>
       <c r="G16">
-        <v>-8.615499060829347</v>
+        <v>-7.423401737289047</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.2146650773015925</v>
       </c>
       <c r="E17">
-        <v>-25.65503907509026</v>
+        <v>-27.96288528361931</v>
       </c>
       <c r="F17">
-        <v>4.388146115400634</v>
+        <v>2.866140297662545</v>
       </c>
       <c r="G17">
-        <v>-8.025381207027893</v>
+        <v>-7.781806287005633</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.02413735114470778</v>
       </c>
       <c r="E18">
-        <v>-24.75983221935796</v>
+        <v>-28.24728703672303</v>
       </c>
       <c r="F18">
-        <v>4.974625266378267</v>
+        <v>2.271687282065564</v>
       </c>
       <c r="G18">
-        <v>-7.002647415499891</v>
+        <v>-6.748963051852982</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3298529003420757</v>
       </c>
       <c r="E19">
-        <v>-25.68306580072374</v>
+        <v>-29.19948926631588</v>
       </c>
       <c r="F19">
-        <v>4.870650246713678</v>
+        <v>2.14746530634175</v>
       </c>
       <c r="G19">
-        <v>-7.594553535051242</v>
+        <v>-6.454831070042799</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.6887397032352265</v>
       </c>
       <c r="E20">
-        <v>-28.07414083303975</v>
+        <v>-27.9077375271539</v>
       </c>
       <c r="F20">
-        <v>4.734930531439008</v>
+        <v>3.010294449832521</v>
       </c>
       <c r="G20">
-        <v>-7.460085794323638</v>
+        <v>-6.174916621249689</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.087544671985989</v>
       </c>
       <c r="E21">
-        <v>-28.47437642278567</v>
+        <v>-29.73213064333506</v>
       </c>
       <c r="F21">
-        <v>4.580824373291799</v>
+        <v>2.355314284847785</v>
       </c>
       <c r="G21">
-        <v>-6.054617195215767</v>
+        <v>-5.466156358301833</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.511474592458483</v>
       </c>
       <c r="E22">
-        <v>-28.91212589121114</v>
+        <v>-30.10219980347889</v>
       </c>
       <c r="F22">
-        <v>4.997377205463558</v>
+        <v>2.747105558615062</v>
       </c>
       <c r="G22">
-        <v>-5.251633373966897</v>
+        <v>-6.036468758770479</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.952432139940245</v>
       </c>
       <c r="E23">
-        <v>-28.90689550373228</v>
+        <v>-31.23218765837587</v>
       </c>
       <c r="F23">
-        <v>4.368666227556401</v>
+        <v>3.65935178788724</v>
       </c>
       <c r="G23">
-        <v>-5.014174650931443</v>
+        <v>-6.204785581105314</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.40185943701914</v>
       </c>
       <c r="E24">
-        <v>-28.86195039920615</v>
+        <v>-30.71424570798558</v>
       </c>
       <c r="F24">
-        <v>4.614300356773732</v>
+        <v>2.974162720457212</v>
       </c>
       <c r="G24">
-        <v>-4.235383276240358</v>
+        <v>-4.865190786024855</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.852619048565191</v>
       </c>
       <c r="E25">
-        <v>-29.61644171786111</v>
+        <v>-31.90021682280238</v>
       </c>
       <c r="F25">
-        <v>4.454039428823723</v>
+        <v>2.563320653160353</v>
       </c>
       <c r="G25">
-        <v>-4.024955256411609</v>
+        <v>-4.315461488398606</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.297280206346009</v>
       </c>
       <c r="E26">
-        <v>-30.04605351849479</v>
+        <v>-31.77102851631156</v>
       </c>
       <c r="F26">
-        <v>4.884647999086185</v>
+        <v>2.921611092423611</v>
       </c>
       <c r="G26">
-        <v>-3.999105792966303</v>
+        <v>-4.175537076217646</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.728083485134424</v>
       </c>
       <c r="E27">
-        <v>-30.29787969382433</v>
+        <v>-31.46833172821685</v>
       </c>
       <c r="F27">
-        <v>4.483156543032126</v>
+        <v>3.439012685681794</v>
       </c>
       <c r="G27">
-        <v>-2.660980985144476</v>
+        <v>-2.858444898591858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.142036826935917</v>
       </c>
       <c r="E28">
-        <v>-30.24367612418953</v>
+        <v>-28.82108997823494</v>
       </c>
       <c r="F28">
-        <v>5.017803088881788</v>
+        <v>3.523463085662398</v>
       </c>
       <c r="G28">
-        <v>-2.408559891797953</v>
+        <v>-2.691821186581696</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.534880213947989</v>
       </c>
       <c r="E29">
-        <v>-29.92926417383697</v>
+        <v>-31.07251366486541</v>
       </c>
       <c r="F29">
-        <v>4.40146626323765</v>
+        <v>2.420594606392803</v>
       </c>
       <c r="G29">
-        <v>-3.575608369953452</v>
+        <v>-3.206188759461809</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.90188547136703</v>
       </c>
       <c r="E30">
-        <v>-28.40433904378304</v>
+        <v>-31.02402502942828</v>
       </c>
       <c r="F30">
-        <v>4.59156001483208</v>
+        <v>3.112554748973314</v>
       </c>
       <c r="G30">
-        <v>-2.717224403894917</v>
+        <v>-2.786477866128557</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.235530488970221</v>
       </c>
       <c r="E31">
-        <v>-29.82702934463981</v>
+        <v>-30.10231301532908</v>
       </c>
       <c r="F31">
-        <v>4.536626002148028</v>
+        <v>2.696482369895179</v>
       </c>
       <c r="G31">
-        <v>-2.881049233914873</v>
+        <v>-3.676794680403608</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.528093052503039</v>
       </c>
       <c r="E32">
-        <v>-28.32779424763139</v>
+        <v>-29.55042562377729</v>
       </c>
       <c r="F32">
-        <v>4.249797161989477</v>
+        <v>2.38875216342919</v>
       </c>
       <c r="G32">
-        <v>-3.726042534789314</v>
+        <v>-1.248697288857638</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.775234029934209</v>
       </c>
       <c r="E33">
-        <v>-30.00747091994944</v>
+        <v>-30.07759660419522</v>
       </c>
       <c r="F33">
-        <v>4.675952429094488</v>
+        <v>1.909269916401558</v>
       </c>
       <c r="G33">
-        <v>-4.217654836154678</v>
+        <v>-1.959718313459951</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.971507535034267</v>
       </c>
       <c r="E34">
-        <v>-28.36972791694242</v>
+        <v>-28.43470246200447</v>
       </c>
       <c r="F34">
-        <v>4.705082797181336</v>
+        <v>2.705059285983765</v>
       </c>
       <c r="G34">
-        <v>-3.394553845524852</v>
+        <v>-2.148336053583071</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.11157082468341</v>
       </c>
       <c r="E35">
-        <v>-28.34955809371226</v>
+        <v>-28.29897956752059</v>
       </c>
       <c r="F35">
-        <v>4.205192890818335</v>
+        <v>2.345296009478328</v>
       </c>
       <c r="G35">
-        <v>-3.331528141811038</v>
+        <v>-2.668718105581646</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.189117002593291</v>
       </c>
       <c r="E36">
-        <v>-28.02917761461759</v>
+        <v>-28.61232279800733</v>
       </c>
       <c r="F36">
-        <v>4.785976187534319</v>
+        <v>2.62624841128142</v>
       </c>
       <c r="G36">
-        <v>-3.617056760692358</v>
+        <v>-3.076521445875673</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.200511673328317</v>
       </c>
       <c r="E37">
-        <v>-27.66625212222087</v>
+        <v>-27.61374899457594</v>
       </c>
       <c r="F37">
-        <v>4.579144444198922</v>
+        <v>2.628602631440176</v>
       </c>
       <c r="G37">
-        <v>-5.224245017610212</v>
+        <v>-4.317604126076923</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.148477337788743</v>
       </c>
       <c r="E38">
-        <v>-25.93912383501345</v>
+        <v>-27.33145751035979</v>
       </c>
       <c r="F38">
-        <v>5.049425186116257</v>
+        <v>2.686793784752036</v>
       </c>
       <c r="G38">
-        <v>-4.698380044385805</v>
+        <v>-4.993348737693647</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.035957424632113</v>
       </c>
       <c r="E39">
-        <v>-28.34977093199062</v>
+        <v>-28.00120070219821</v>
       </c>
       <c r="F39">
-        <v>5.637793014772273</v>
+        <v>3.175379789536434</v>
       </c>
       <c r="G39">
-        <v>-4.665518610467966</v>
+        <v>-4.797630434115888</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.868089882304234</v>
       </c>
       <c r="E40">
-        <v>-26.07415840144817</v>
+        <v>-26.08354592806607</v>
       </c>
       <c r="F40">
-        <v>5.292055655131038</v>
+        <v>3.394133396532922</v>
       </c>
       <c r="G40">
-        <v>-5.549824226846114</v>
+        <v>-6.527096693668009</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.650281672399083</v>
       </c>
       <c r="E41">
-        <v>-27.25047933815463</v>
+        <v>-25.7544798358247</v>
       </c>
       <c r="F41">
-        <v>5.177147842484302</v>
+        <v>3.556934098939915</v>
       </c>
       <c r="G41">
-        <v>-6.016535337796852</v>
+        <v>-4.958026387606224</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.391599843174591</v>
       </c>
       <c r="E42">
-        <v>-25.14756922084271</v>
+        <v>-24.45426437874238</v>
       </c>
       <c r="F42">
-        <v>5.28565900204662</v>
+        <v>3.602270646895132</v>
       </c>
       <c r="G42">
-        <v>-5.646203547711683</v>
+        <v>-5.203940818600368</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.10575244273044</v>
       </c>
       <c r="E43">
-        <v>-24.92058851815625</v>
+        <v>-20.75040284549876</v>
       </c>
       <c r="F43">
-        <v>5.411295829294415</v>
+        <v>3.946154120288901</v>
       </c>
       <c r="G43">
-        <v>-5.477919537592443</v>
+        <v>-5.570217018838063</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.803661647568098</v>
       </c>
       <c r="E44">
-        <v>-25.18242488527975</v>
+        <v>-22.21484794094325</v>
       </c>
       <c r="F44">
-        <v>5.437405969830656</v>
+        <v>3.144829599721188</v>
       </c>
       <c r="G44">
-        <v>-5.98434327307714</v>
+        <v>-4.71713878804115</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.495078931630998</v>
       </c>
       <c r="E45">
-        <v>-23.73614349908003</v>
+        <v>-24.07946975597156</v>
       </c>
       <c r="F45">
-        <v>5.58454555812032</v>
+        <v>3.961227093550241</v>
       </c>
       <c r="G45">
-        <v>-6.280135552996402</v>
+        <v>-6.228948496669065</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.186586934654133</v>
       </c>
       <c r="E46">
-        <v>-22.44226337713445</v>
+        <v>-21.22273174144679</v>
       </c>
       <c r="F46">
-        <v>6.193874395536775</v>
+        <v>3.010067477164154</v>
       </c>
       <c r="G46">
-        <v>-6.844499098777774</v>
+        <v>-5.615058192669435</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.886741749908057</v>
       </c>
       <c r="E47">
-        <v>-22.80099097412606</v>
+        <v>-22.34343396039105</v>
       </c>
       <c r="F47">
-        <v>6.0810855467064</v>
+        <v>3.719875623805383</v>
       </c>
       <c r="G47">
-        <v>-7.360018380425253</v>
+        <v>-5.857842338295868</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.604566740677315</v>
       </c>
       <c r="E48">
-        <v>-21.52579080746212</v>
+        <v>-23.06875058525159</v>
       </c>
       <c r="F48">
-        <v>5.996247470781286</v>
+        <v>4.072662390044442</v>
       </c>
       <c r="G48">
-        <v>-7.402119734254488</v>
+        <v>-7.195694804728261</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.344227628202794</v>
       </c>
       <c r="E49">
-        <v>-21.11969084387626</v>
+        <v>-21.49377449622789</v>
       </c>
       <c r="F49">
-        <v>6.002152073628441</v>
+        <v>4.659572292071531</v>
       </c>
       <c r="G49">
-        <v>-8.741212502436351</v>
+        <v>-7.389956245933626</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.107853800413328</v>
       </c>
       <c r="E50">
-        <v>-20.28967137148437</v>
+        <v>-19.57462079719921</v>
       </c>
       <c r="F50">
-        <v>6.291626719271534</v>
+        <v>4.847855232523441</v>
       </c>
       <c r="G50">
-        <v>-7.844674492084594</v>
+        <v>-7.079621592062905</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.894542495683038</v>
       </c>
       <c r="E51">
-        <v>-20.13077174702923</v>
+        <v>-17.72777777112502</v>
       </c>
       <c r="F51">
-        <v>6.041241074631744</v>
+        <v>4.551554839481281</v>
       </c>
       <c r="G51">
-        <v>-5.925648781821793</v>
+        <v>-6.560788276640388</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.706570474511671</v>
       </c>
       <c r="E52">
-        <v>-18.81923057645373</v>
+        <v>-20.04385674540001</v>
       </c>
       <c r="F52">
-        <v>6.483721806511128</v>
+        <v>4.50579085394622</v>
       </c>
       <c r="G52">
-        <v>-8.377955026033346</v>
+        <v>-7.784080173546329</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.544807130159761</v>
       </c>
       <c r="E53">
-        <v>-19.37543133949783</v>
+        <v>-16.9501074582618</v>
       </c>
       <c r="F53">
-        <v>6.532358570199098</v>
+        <v>5.26262044783996</v>
       </c>
       <c r="G53">
-        <v>-8.18624309397967</v>
+        <v>-9.143857762438932</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.4074383129906</v>
       </c>
       <c r="E54">
-        <v>-17.4399524916715</v>
+        <v>-17.00752398020505</v>
       </c>
       <c r="F54">
-        <v>6.418819220501787</v>
+        <v>3.852097971905434</v>
       </c>
       <c r="G54">
-        <v>-8.275151073354385</v>
+        <v>-8.278005736111101</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.291482482554711</v>
       </c>
       <c r="E55">
-        <v>-15.38814620353614</v>
+        <v>-15.23215838786792</v>
       </c>
       <c r="F55">
-        <v>6.622559496689936</v>
+        <v>4.722473542435709</v>
       </c>
       <c r="G55">
-        <v>-7.137302185856384</v>
+        <v>-8.08283867775533</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.192996952203717</v>
       </c>
       <c r="E56">
-        <v>-14.96097072191858</v>
+        <v>-15.81221515198443</v>
       </c>
       <c r="F56">
-        <v>6.490101892247489</v>
+        <v>5.258558134096631</v>
       </c>
       <c r="G56">
-        <v>-9.031134676985769</v>
+        <v>-9.639384561124713</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.112504186482161</v>
       </c>
       <c r="E57">
-        <v>-16.74338714828565</v>
+        <v>-15.42416115731914</v>
       </c>
       <c r="F57">
-        <v>6.971953270047129</v>
+        <v>4.64210202354649</v>
       </c>
       <c r="G57">
-        <v>-8.543673120893102</v>
+        <v>-9.17335594425834</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.049204225437998</v>
       </c>
       <c r="E58">
-        <v>-15.77874972906774</v>
+        <v>-14.45081095411047</v>
       </c>
       <c r="F58">
-        <v>7.055805588762912</v>
+        <v>4.556420669605325</v>
       </c>
       <c r="G58">
-        <v>-9.009609863555811</v>
+        <v>-9.592210438764576</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.001807048558998</v>
       </c>
       <c r="E59">
-        <v>-14.70022571703093</v>
+        <v>-13.8385386259034</v>
       </c>
       <c r="F59">
-        <v>6.56090742436918</v>
+        <v>4.335123974682243</v>
       </c>
       <c r="G59">
-        <v>-9.551247668816469</v>
+        <v>-9.047458754244007</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.968660084029128</v>
       </c>
       <c r="E60">
-        <v>-13.98906963039237</v>
+        <v>-15.28578004859275</v>
       </c>
       <c r="F60">
-        <v>6.882767921992122</v>
+        <v>5.517063436018661</v>
       </c>
       <c r="G60">
-        <v>-8.405884783947339</v>
+        <v>-9.823953273843479</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.948444650326174</v>
       </c>
       <c r="E61">
-        <v>-14.45241403390919</v>
+        <v>-12.94715380223357</v>
       </c>
       <c r="F61">
-        <v>6.700949560751659</v>
+        <v>4.507595038149517</v>
       </c>
       <c r="G61">
-        <v>-8.63900245085965</v>
+        <v>-10.32505814918032</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.944241858439581</v>
       </c>
       <c r="E62">
-        <v>-14.31657792757511</v>
+        <v>-13.61600941316648</v>
       </c>
       <c r="F62">
-        <v>6.744776823298976</v>
+        <v>4.942342131956365</v>
       </c>
       <c r="G62">
-        <v>-8.426700853520456</v>
+        <v>-9.184708970854018</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.957310362893383</v>
       </c>
       <c r="E63">
-        <v>-12.92064864386667</v>
+        <v>-13.13269443927584</v>
       </c>
       <c r="F63">
-        <v>6.464727341964935</v>
+        <v>4.945100595407687</v>
       </c>
       <c r="G63">
-        <v>-8.517111632369398</v>
+        <v>-10.11105687907333</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.988689196165051</v>
       </c>
       <c r="E64">
-        <v>-14.32061279791594</v>
+        <v>-12.45903411742079</v>
       </c>
       <c r="F64">
-        <v>6.363535636773753</v>
+        <v>4.52461301807263</v>
       </c>
       <c r="G64">
-        <v>-8.826776917041991</v>
+        <v>-9.771854037922616</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.037510564675262</v>
       </c>
       <c r="E65">
-        <v>-12.44874089600135</v>
+        <v>-10.79414064850078</v>
       </c>
       <c r="F65">
-        <v>6.721763120114399</v>
+        <v>4.847265434932648</v>
       </c>
       <c r="G65">
-        <v>-8.498264295731946</v>
+        <v>-10.2112555418341</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.104665928001444</v>
       </c>
       <c r="E66">
-        <v>-14.81466478367877</v>
+        <v>-13.34373944192931</v>
       </c>
       <c r="F66">
-        <v>6.447452568146955</v>
+        <v>4.689544281439622</v>
       </c>
       <c r="G66">
-        <v>-8.148528733375413</v>
+        <v>-9.033480750400772</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.192112950770115</v>
       </c>
       <c r="E67">
-        <v>-13.17155780320967</v>
+        <v>-11.05901562168343</v>
       </c>
       <c r="F67">
-        <v>6.190183190389901</v>
+        <v>4.545991524004079</v>
       </c>
       <c r="G67">
-        <v>-8.892575252973536</v>
+        <v>-10.71287228773421</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.299500669680767</v>
       </c>
       <c r="E68">
-        <v>-13.80653590009119</v>
+        <v>-11.79960226089784</v>
       </c>
       <c r="F68">
-        <v>5.949459623136364</v>
+        <v>5.047640882730627</v>
       </c>
       <c r="G68">
-        <v>-8.172970552771716</v>
+        <v>-10.10178414694634</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.425426413384379</v>
       </c>
       <c r="E69">
-        <v>-14.46194194322133</v>
+        <v>-12.94636131928223</v>
       </c>
       <c r="F69">
-        <v>6.274287332796135</v>
+        <v>4.082099151497134</v>
       </c>
       <c r="G69">
-        <v>-7.652693499863044</v>
+        <v>-8.940212027573555</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.564731161369327</v>
       </c>
       <c r="E70">
-        <v>-12.7541185407086</v>
+        <v>-11.77741726673426</v>
       </c>
       <c r="F70">
-        <v>5.971273850321687</v>
+        <v>4.689527714091566</v>
       </c>
       <c r="G70">
-        <v>-7.335740622106921</v>
+        <v>-7.760311004569711</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.715821304053951</v>
       </c>
       <c r="E71">
-        <v>-12.0179018789116</v>
+        <v>-10.48016343165297</v>
       </c>
       <c r="F71">
-        <v>5.912767917396763</v>
+        <v>4.304302080358879</v>
       </c>
       <c r="G71">
-        <v>-7.130582244102641</v>
+        <v>-9.89208127708223</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.875977798972337</v>
       </c>
       <c r="E72">
-        <v>-14.25576957860011</v>
+        <v>-12.88917122103936</v>
       </c>
       <c r="F72">
-        <v>5.935518199747249</v>
+        <v>4.6937391339674</v>
       </c>
       <c r="G72">
-        <v>-7.23594554959797</v>
+        <v>-7.920188525053654</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.040613319441045</v>
       </c>
       <c r="E73">
-        <v>-12.80121467038838</v>
+        <v>-13.50583164055986</v>
       </c>
       <c r="F73">
-        <v>5.202529019706078</v>
+        <v>4.005493390821042</v>
       </c>
       <c r="G73">
-        <v>-7.557482293872636</v>
+        <v>-8.209093520919643</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.203867598279914</v>
       </c>
       <c r="E74">
-        <v>-12.94253928721975</v>
+        <v>-11.71362918186222</v>
       </c>
       <c r="F74">
-        <v>5.387157203176837</v>
+        <v>3.66575506791088</v>
       </c>
       <c r="G74">
-        <v>-6.427767554620498</v>
+        <v>-8.939273598207555</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.35748731501742</v>
       </c>
       <c r="E75">
-        <v>-13.04347897285072</v>
+        <v>-10.66760149930445</v>
       </c>
       <c r="F75">
-        <v>5.361505978181748</v>
+        <v>5.249711170234733</v>
       </c>
       <c r="G75">
-        <v>-7.468069006377767</v>
+        <v>-6.606948501538656</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.497083495314099</v>
       </c>
       <c r="E76">
-        <v>-12.35594793511018</v>
+        <v>-12.54640649492478</v>
       </c>
       <c r="F76">
-        <v>5.871873075455357</v>
+        <v>3.77381393887127</v>
       </c>
       <c r="G76">
-        <v>-6.767679139628055</v>
+        <v>-7.678339527571663</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.617663311222697</v>
       </c>
       <c r="E77">
-        <v>-11.83913131051079</v>
+        <v>-11.5734004557407</v>
       </c>
       <c r="F77">
-        <v>4.994572353437679</v>
+        <v>4.103326894561274</v>
       </c>
       <c r="G77">
-        <v>-6.594348610750388</v>
+        <v>-5.532962029252127</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.714358656192315</v>
       </c>
       <c r="E78">
-        <v>-13.27484776685062</v>
+        <v>-12.7016878686478</v>
       </c>
       <c r="F78">
-        <v>5.153501266603986</v>
+        <v>4.269807204971502</v>
       </c>
       <c r="G78">
-        <v>-6.887171385158354</v>
+        <v>-5.291723338980193</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.782713819290299</v>
       </c>
       <c r="E79">
-        <v>-14.5608166447048</v>
+        <v>-12.65825074596622</v>
       </c>
       <c r="F79">
-        <v>4.666353307630848</v>
+        <v>3.375664116920104</v>
       </c>
       <c r="G79">
-        <v>-5.648018063234057</v>
+        <v>-7.20261818221869</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.818964360261436</v>
       </c>
       <c r="E80">
-        <v>-15.49904400350998</v>
+        <v>-14.34318724084418</v>
       </c>
       <c r="F80">
-        <v>4.469619362935576</v>
+        <v>3.647449805043816</v>
       </c>
       <c r="G80">
-        <v>-3.665284155173076</v>
+        <v>-5.330956905166473</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.824071798202803</v>
       </c>
       <c r="E81">
-        <v>-15.75067771869419</v>
+        <v>-13.12984602912501</v>
       </c>
       <c r="F81">
-        <v>5.026250779655538</v>
+        <v>3.281006573802205</v>
       </c>
       <c r="G81">
-        <v>-5.449619001642231</v>
+        <v>-5.885001009143392</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.799284541768586</v>
       </c>
       <c r="E82">
-        <v>-16.37827893141723</v>
+        <v>-14.92929404623493</v>
       </c>
       <c r="F82">
-        <v>4.820830574374511</v>
+        <v>3.494037818780154</v>
       </c>
       <c r="G82">
-        <v>-4.70378093507265</v>
+        <v>-4.877328024573241</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.746552560409087</v>
       </c>
       <c r="E83">
-        <v>-16.38535693629122</v>
+        <v>-14.27653263192528</v>
       </c>
       <c r="F83">
-        <v>5.067713881635264</v>
+        <v>3.328718879468651</v>
       </c>
       <c r="G83">
-        <v>-3.744778309893743</v>
+        <v>-5.359887435656097</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.667769969674711</v>
       </c>
       <c r="E84">
-        <v>-17.39825430300887</v>
+        <v>-15.97515870372842</v>
       </c>
       <c r="F84">
-        <v>4.170401459900756</v>
+        <v>3.000468355700513</v>
       </c>
       <c r="G84">
-        <v>-4.497228037905606</v>
+        <v>-6.003095454289366</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.566319989031063</v>
       </c>
       <c r="E85">
-        <v>-17.99824540970714</v>
+        <v>-17.90514904105745</v>
       </c>
       <c r="F85">
-        <v>4.549114469112634</v>
+        <v>2.987615407078676</v>
       </c>
       <c r="G85">
-        <v>-4.273291228916623</v>
+        <v>-3.208646394409834</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.450803075532421</v>
       </c>
       <c r="E86">
-        <v>-19.33354748340088</v>
+        <v>-17.14890746719852</v>
       </c>
       <c r="F86">
-        <v>4.127742195391387</v>
+        <v>2.212099501312585</v>
       </c>
       <c r="G86">
-        <v>-3.658019530640466</v>
+        <v>-5.137886547387186</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.329322224894286</v>
       </c>
       <c r="E87">
-        <v>-19.10262700832775</v>
+        <v>-20.06377297408574</v>
       </c>
       <c r="F87">
-        <v>4.272118350025313</v>
+        <v>2.229130735114142</v>
       </c>
       <c r="G87">
-        <v>-3.922312083589059</v>
+        <v>-3.411685103286713</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.210463598815836</v>
       </c>
       <c r="E88">
-        <v>-21.29189965343995</v>
+        <v>-20.98204787641312</v>
       </c>
       <c r="F88">
-        <v>3.838315595057656</v>
+        <v>2.632080117797128</v>
       </c>
       <c r="G88">
-        <v>-3.671823629741049</v>
+        <v>-2.745774312683646</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.100922963162209</v>
       </c>
       <c r="E89">
-        <v>-21.09593899770603</v>
+        <v>-21.33475260297454</v>
       </c>
       <c r="F89">
-        <v>4.279588567263758</v>
+        <v>2.243337236072154</v>
       </c>
       <c r="G89">
-        <v>-3.461421859684776</v>
+        <v>-3.927762192599297</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.008536532314583</v>
       </c>
       <c r="E90">
-        <v>-24.65074128051318</v>
+        <v>-25.53796443656996</v>
       </c>
       <c r="F90">
-        <v>3.334308702702742</v>
+        <v>1.34312055822343</v>
       </c>
       <c r="G90">
-        <v>-3.16564926709487</v>
+        <v>-1.945343281808023</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.944176347199905</v>
       </c>
       <c r="E91">
-        <v>-25.51841048580484</v>
+        <v>-24.5153217937878</v>
       </c>
       <c r="F91">
-        <v>3.075824938333184</v>
+        <v>1.688559705599658</v>
       </c>
       <c r="G91">
-        <v>-3.874498123024831</v>
+        <v>-1.437331435088555</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.915012148122798</v>
       </c>
       <c r="E92">
-        <v>-27.74506568385036</v>
+        <v>-26.84808819478106</v>
       </c>
       <c r="F92">
-        <v>3.011520433588664</v>
+        <v>1.485767081720311</v>
       </c>
       <c r="G92">
-        <v>-2.835046507651458</v>
+        <v>-2.342223435530659</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.926732729205357</v>
       </c>
       <c r="E93">
-        <v>-26.32229160622446</v>
+        <v>-26.49205051135</v>
       </c>
       <c r="F93">
-        <v>2.702769678482427</v>
+        <v>0.8352899219371933</v>
       </c>
       <c r="G93">
-        <v>-2.487381396098934</v>
+        <v>-2.941955268501286</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.979833317099112</v>
       </c>
       <c r="E94">
-        <v>-30.49739293741727</v>
+        <v>-29.94218843865486</v>
       </c>
       <c r="F94">
-        <v>2.817872985836224</v>
+        <v>1.213893586651902</v>
       </c>
       <c r="G94">
-        <v>-3.047577790499811</v>
+        <v>-2.687867314602566</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.077771203490882</v>
       </c>
       <c r="E95">
-        <v>-31.52585014082528</v>
+        <v>-32.22438763464147</v>
       </c>
       <c r="F95">
-        <v>2.097108851925568</v>
+        <v>0.128366150592512</v>
       </c>
       <c r="G95">
-        <v>-2.814049970892571</v>
+        <v>-1.803847164500089</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.224729385924654</v>
       </c>
       <c r="E96">
-        <v>-33.90024001066003</v>
+        <v>-34.46672040970154</v>
       </c>
       <c r="F96">
-        <v>1.753223721796993</v>
+        <v>0.3878969713592084</v>
       </c>
       <c r="G96">
-        <v>-2.285356584683923</v>
+        <v>-3.655315804075483</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.4158360222791</v>
       </c>
       <c r="E97">
-        <v>-36.56133889110542</v>
+        <v>-34.96628807680572</v>
       </c>
       <c r="F97">
-        <v>1.089381682337108</v>
+        <v>-0.642053638911557</v>
       </c>
       <c r="G97">
-        <v>-2.798385419167782</v>
+        <v>-2.464452219841534</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.651100867866574</v>
       </c>
       <c r="E98">
-        <v>-37.21456447400086</v>
+        <v>-37.57364982043908</v>
       </c>
       <c r="F98">
-        <v>0.411969328084562</v>
+        <v>-1.078020089535326</v>
       </c>
       <c r="G98">
-        <v>-4.113666362492756</v>
+        <v>-5.290584755099065</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.911771426366706</v>
       </c>
       <c r="E99">
-        <v>-40.50040030735943</v>
+        <v>-40.73825840461232</v>
       </c>
       <c r="F99">
-        <v>0.0238676027293544</v>
+        <v>-0.4861118185997444</v>
       </c>
       <c r="G99">
-        <v>-2.55831156254945</v>
+        <v>-0.97515169111141</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.203938613554773</v>
       </c>
       <c r="E100">
-        <v>-43.44536658097563</v>
+        <v>-42.94586457674457</v>
       </c>
       <c r="F100">
-        <v>0.1114508882273461</v>
+        <v>-1.202608203651177</v>
       </c>
       <c r="G100">
-        <v>-3.365921906197137</v>
+        <v>-3.784520465421738</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.496973231748146</v>
       </c>
       <c r="E101">
-        <v>-44.43562610612894</v>
+        <v>-46.00012104206189</v>
       </c>
       <c r="F101">
-        <v>-0.1572267654010623</v>
+        <v>-1.657292444108603</v>
       </c>
       <c r="G101">
-        <v>-3.496839365197423</v>
+        <v>-6.538712217988444</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.81383859159558</v>
       </c>
       <c r="E102">
-        <v>-46.78441198392433</v>
+        <v>-46.05194942707968</v>
       </c>
       <c r="F102">
-        <v>-0.5554221475593819</v>
+        <v>-2.115984326060773</v>
       </c>
       <c r="G102">
-        <v>-4.29073748394819</v>
+        <v>-3.72305334194866</v>
       </c>
     </row>
   </sheetData>
